--- a/backend/exports/enquiries.xlsx
+++ b/backend/exports/enquiries.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="53">
   <si>
     <t>S.No</t>
   </si>
@@ -68,6 +68,108 @@
   </si>
   <si>
     <t>6/6/2026, 10:57:13 pm</t>
+  </si>
+  <si>
+    <t>Test User</t>
+  </si>
+  <si>
+    <t>testnew@example.com</t>
+  </si>
+  <si>
+    <t>9876543210</t>
+  </si>
+  <si>
+    <t>Java Full Stack</t>
+  </si>
+  <si>
+    <t>Testing production enquiry</t>
+  </si>
+  <si>
+    <t>49.205.253.208</t>
+  </si>
+  <si>
+    <t>6/6/2026, 11:10:49 pm</t>
+  </si>
+  <si>
+    <t>siva</t>
+  </si>
+  <si>
+    <t>siva46@gmil.com</t>
+  </si>
+  <si>
+    <t>9458765489</t>
+  </si>
+  <si>
+    <t>AI &amp; Machine Learning</t>
+  </si>
+  <si>
+    <t>tesing the email trigger</t>
+  </si>
+  <si>
+    <t>6/6/2026, 11:24:33 pm</t>
+  </si>
+  <si>
+    <t>lava</t>
+  </si>
+  <si>
+    <t>lava@gmail.com</t>
+  </si>
+  <si>
+    <t>9456845789</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>6/6/2026, 11:30:41 pm</t>
+  </si>
+  <si>
+    <t>gama</t>
+  </si>
+  <si>
+    <t>gama@gmail.com</t>
+  </si>
+  <si>
+    <t>9874565498</t>
+  </si>
+  <si>
+    <t>tesing-03</t>
+  </si>
+  <si>
+    <t>6/6/2026, 11:31:38 pm</t>
+  </si>
+  <si>
+    <t>Live Domain Test</t>
+  </si>
+  <si>
+    <t>livetesting@example.com</t>
+  </si>
+  <si>
+    <t>9876543212</t>
+  </si>
+  <si>
+    <t>Testing from live domain CORS</t>
+  </si>
+  <si>
+    <t>6/6/2026, 11:35:43 pm</t>
+  </si>
+  <si>
+    <t>Arudra Sunkari</t>
+  </si>
+  <si>
+    <t>arudrasunkari@gmail.com</t>
+  </si>
+  <si>
+    <t>9553729135</t>
+  </si>
+  <si>
+    <t>Digital Marketing</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>6/6/2026, 11:37:14 pm</t>
   </si>
 </sst>
 </file>
@@ -454,7 +556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -532,6 +634,198 @@
         <v>18</v>
       </c>
     </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" t="s">
+        <v>24</v>
+      </c>
+      <c r="J4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" t="s">
+        <v>24</v>
+      </c>
+      <c r="J5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" t="s">
+        <v>40</v>
+      </c>
+      <c r="G6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I7" t="s">
+        <v>24</v>
+      </c>
+      <c r="J7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8" t="s">
+        <v>49</v>
+      </c>
+      <c r="E8" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" t="s">
+        <v>51</v>
+      </c>
+      <c r="G8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" t="s">
+        <v>17</v>
+      </c>
+      <c r="J8" t="s">
+        <v>52</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/backend/exports/enquiries.xlsx
+++ b/backend/exports/enquiries.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="79">
   <si>
     <t>S.No</t>
   </si>
@@ -170,6 +170,84 @@
   </si>
   <si>
     <t>6/6/2026, 11:37:14 pm</t>
+  </si>
+  <si>
+    <t>6/6/2026, 11:37:32 pm</t>
+  </si>
+  <si>
+    <t>Domain Test</t>
+  </si>
+  <si>
+    <t>domaintest@example.com</t>
+  </si>
+  <si>
+    <t>9876543213</t>
+  </si>
+  <si>
+    <t>Testing deployed domain</t>
+  </si>
+  <si>
+    <t>6/6/2026, 11:39:26 pm</t>
+  </si>
+  <si>
+    <t>eswar</t>
+  </si>
+  <si>
+    <t>eswar@gmail.com</t>
+  </si>
+  <si>
+    <t>9440354687</t>
+  </si>
+  <si>
+    <t>test001</t>
+  </si>
+  <si>
+    <t>6/6/2026, 11:48:23 pm</t>
+  </si>
+  <si>
+    <t>hello</t>
+  </si>
+  <si>
+    <t>hello@gmail.com</t>
+  </si>
+  <si>
+    <t>9487548657</t>
+  </si>
+  <si>
+    <t>Data Analytics</t>
+  </si>
+  <si>
+    <t>test004</t>
+  </si>
+  <si>
+    <t>6/6/2026, 11:57:24 pm</t>
+  </si>
+  <si>
+    <t>hell</t>
+  </si>
+  <si>
+    <t>9485675689</t>
+  </si>
+  <si>
+    <t>test007</t>
+  </si>
+  <si>
+    <t>6/6/2026, 11:58:17 pm</t>
+  </si>
+  <si>
+    <t>local</t>
+  </si>
+  <si>
+    <t>local@gmail.com</t>
+  </si>
+  <si>
+    <t>9874587465</t>
+  </si>
+  <si>
+    <t>local check</t>
+  </si>
+  <si>
+    <t>7/6/2026, 12:15:29 am</t>
   </si>
 </sst>
 </file>
@@ -556,7 +634,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -826,6 +904,198 @@
         <v>52</v>
       </c>
     </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" t="s">
+        <v>44</v>
+      </c>
+      <c r="E9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F9" t="s">
+        <v>45</v>
+      </c>
+      <c r="G9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I9" t="s">
+        <v>24</v>
+      </c>
+      <c r="J9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" t="s">
+        <v>57</v>
+      </c>
+      <c r="G10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" t="s">
+        <v>16</v>
+      </c>
+      <c r="I10" t="s">
+        <v>24</v>
+      </c>
+      <c r="J10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>59</v>
+      </c>
+      <c r="C11" t="s">
+        <v>60</v>
+      </c>
+      <c r="D11" t="s">
+        <v>61</v>
+      </c>
+      <c r="E11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" t="s">
+        <v>62</v>
+      </c>
+      <c r="G11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" t="s">
+        <v>16</v>
+      </c>
+      <c r="I11" t="s">
+        <v>24</v>
+      </c>
+      <c r="J11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>64</v>
+      </c>
+      <c r="C12" t="s">
+        <v>65</v>
+      </c>
+      <c r="D12" t="s">
+        <v>66</v>
+      </c>
+      <c r="E12" t="s">
+        <v>67</v>
+      </c>
+      <c r="F12" t="s">
+        <v>68</v>
+      </c>
+      <c r="G12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I12" t="s">
+        <v>24</v>
+      </c>
+      <c r="J12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C13" t="s">
+        <v>65</v>
+      </c>
+      <c r="D13" t="s">
+        <v>71</v>
+      </c>
+      <c r="E13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" t="s">
+        <v>72</v>
+      </c>
+      <c r="G13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H13" t="s">
+        <v>16</v>
+      </c>
+      <c r="I13" t="s">
+        <v>24</v>
+      </c>
+      <c r="J13" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>74</v>
+      </c>
+      <c r="C14" t="s">
+        <v>75</v>
+      </c>
+      <c r="D14" t="s">
+        <v>76</v>
+      </c>
+      <c r="E14" t="s">
+        <v>50</v>
+      </c>
+      <c r="F14" t="s">
+        <v>77</v>
+      </c>
+      <c r="G14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H14" t="s">
+        <v>16</v>
+      </c>
+      <c r="I14" t="s">
+        <v>17</v>
+      </c>
+      <c r="J14" t="s">
+        <v>78</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/backend/exports/enquiries.xlsx
+++ b/backend/exports/enquiries.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="93">
   <si>
     <t>S.No</t>
   </si>
@@ -248,6 +248,48 @@
   </si>
   <si>
     <t>7/6/2026, 12:15:29 am</t>
+  </si>
+  <si>
+    <t>simple</t>
+  </si>
+  <si>
+    <t>simple@gmail.com</t>
+  </si>
+  <si>
+    <t>9847548657</t>
+  </si>
+  <si>
+    <t>test final</t>
+  </si>
+  <si>
+    <t>7/6/2026, 12:19:18 am</t>
+  </si>
+  <si>
+    <t>random</t>
+  </si>
+  <si>
+    <t>random@gmail.com</t>
+  </si>
+  <si>
+    <t>9845748654</t>
+  </si>
+  <si>
+    <t>Cloud Computing</t>
+  </si>
+  <si>
+    <t>test 004</t>
+  </si>
+  <si>
+    <t>7/6/2026, 12:27:20 am</t>
+  </si>
+  <si>
+    <t>Arudra Siva Sai Sunkari</t>
+  </si>
+  <si>
+    <t>arudrasunkari18@gmail.com</t>
+  </si>
+  <si>
+    <t>7/6/2026, 12:38:23 am</t>
   </si>
 </sst>
 </file>
@@ -634,7 +676,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1096,6 +1138,102 @@
         <v>78</v>
       </c>
     </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>79</v>
+      </c>
+      <c r="C15" t="s">
+        <v>80</v>
+      </c>
+      <c r="D15" t="s">
+        <v>81</v>
+      </c>
+      <c r="E15" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" t="s">
+        <v>82</v>
+      </c>
+      <c r="G15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H15" t="s">
+        <v>16</v>
+      </c>
+      <c r="I15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J15" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>84</v>
+      </c>
+      <c r="C16" t="s">
+        <v>85</v>
+      </c>
+      <c r="D16" t="s">
+        <v>86</v>
+      </c>
+      <c r="E16" t="s">
+        <v>87</v>
+      </c>
+      <c r="F16" t="s">
+        <v>88</v>
+      </c>
+      <c r="G16" t="s">
+        <v>15</v>
+      </c>
+      <c r="H16" t="s">
+        <v>16</v>
+      </c>
+      <c r="I16" t="s">
+        <v>17</v>
+      </c>
+      <c r="J16" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>90</v>
+      </c>
+      <c r="C17" t="s">
+        <v>91</v>
+      </c>
+      <c r="D17" t="s">
+        <v>49</v>
+      </c>
+      <c r="E17" t="s">
+        <v>29</v>
+      </c>
+      <c r="F17" t="s">
+        <v>51</v>
+      </c>
+      <c r="G17" t="s">
+        <v>15</v>
+      </c>
+      <c r="H17" t="s">
+        <v>16</v>
+      </c>
+      <c r="I17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J17" t="s">
+        <v>92</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/backend/exports/enquiries.xlsx
+++ b/backend/exports/enquiries.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="103">
   <si>
     <t>S.No</t>
   </si>
@@ -290,6 +290,36 @@
   </si>
   <si>
     <t>7/6/2026, 12:38:23 am</t>
+  </si>
+  <si>
+    <t>king</t>
+  </si>
+  <si>
+    <t>king@gmail.com</t>
+  </si>
+  <si>
+    <t>9758468459</t>
+  </si>
+  <si>
+    <t>testing</t>
+  </si>
+  <si>
+    <t>7/6/2026, 12:45:18 am</t>
+  </si>
+  <si>
+    <t>hinmk</t>
+  </si>
+  <si>
+    <t>hinkk@gmail.com</t>
+  </si>
+  <si>
+    <t>9451236545</t>
+  </si>
+  <si>
+    <t>enquiry01</t>
+  </si>
+  <si>
+    <t>7/6/2026, 12:50:10 am</t>
   </si>
 </sst>
 </file>
@@ -676,7 +706,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1234,6 +1264,70 @@
         <v>92</v>
       </c>
     </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>93</v>
+      </c>
+      <c r="C18" t="s">
+        <v>94</v>
+      </c>
+      <c r="D18" t="s">
+        <v>95</v>
+      </c>
+      <c r="E18" t="s">
+        <v>22</v>
+      </c>
+      <c r="F18" t="s">
+        <v>96</v>
+      </c>
+      <c r="G18" t="s">
+        <v>15</v>
+      </c>
+      <c r="H18" t="s">
+        <v>16</v>
+      </c>
+      <c r="I18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J18" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>98</v>
+      </c>
+      <c r="C19" t="s">
+        <v>99</v>
+      </c>
+      <c r="D19" t="s">
+        <v>100</v>
+      </c>
+      <c r="E19" t="s">
+        <v>29</v>
+      </c>
+      <c r="F19" t="s">
+        <v>101</v>
+      </c>
+      <c r="G19" t="s">
+        <v>15</v>
+      </c>
+      <c r="H19" t="s">
+        <v>16</v>
+      </c>
+      <c r="I19" t="s">
+        <v>17</v>
+      </c>
+      <c r="J19" t="s">
+        <v>102</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
